--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_17/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_17/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>74.29000000000001</v>
+        <v>75.95</v>
       </c>
       <c r="D2" t="n">
-        <v>13.6</v>
+        <v>12.81</v>
       </c>
       <c r="E2" t="n">
-        <v>18.3</v>
+        <v>16.87</v>
       </c>
       <c r="F2" t="n">
-        <v>55.76</v>
+        <v>58.17</v>
       </c>
       <c r="G2" t="n">
-        <v>62.19</v>
+        <v>64.23</v>
       </c>
       <c r="H2" t="n">
-        <v>71.84</v>
+        <v>74.05</v>
       </c>
       <c r="I2" t="n">
-        <v>84.72</v>
+        <v>86.16</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>44.24</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>48.79</v>
+        <v>45.49</v>
       </c>
       <c r="D3" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>0.95</v>
+        <v>0.49</v>
       </c>
       <c r="F3" t="n">
-        <v>47.35</v>
+        <v>45.42</v>
       </c>
       <c r="G3" t="n">
-        <v>48.79</v>
+        <v>45.42</v>
       </c>
       <c r="H3" t="n">
-        <v>48.81</v>
+        <v>45.42</v>
       </c>
       <c r="I3" t="n">
-        <v>48.88</v>
+        <v>45.43</v>
       </c>
       <c r="J3" t="n">
-        <v>49.95</v>
+        <v>46.28</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>10.42</v>
+        <v>11.06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="E4" t="n">
-        <v>16.1</v>
+        <v>12.83</v>
       </c>
       <c r="F4" t="n">
-        <v>6.88</v>
+        <v>8.07</v>
       </c>
       <c r="G4" t="n">
-        <v>9.08</v>
+        <v>10.13</v>
       </c>
       <c r="H4" t="n">
-        <v>10.75</v>
+        <v>11.34</v>
       </c>
       <c r="I4" t="n">
-        <v>11.93</v>
+        <v>12.38</v>
       </c>
       <c r="J4" t="n">
-        <v>12.51</v>
+        <v>12.78</v>
       </c>
       <c r="K4" t="n">
-        <v>5.63</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>150.51</v>
+        <v>97.42</v>
       </c>
       <c r="D5" t="n">
-        <v>27.31</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>18.14</v>
+        <v>20.53</v>
       </c>
       <c r="F5" t="n">
-        <v>97.18000000000001</v>
+        <v>36.38</v>
       </c>
       <c r="G5" t="n">
-        <v>132.61</v>
+        <v>90.61</v>
       </c>
       <c r="H5" t="n">
-        <v>156.06</v>
+        <v>100.82</v>
       </c>
       <c r="I5" t="n">
-        <v>170.22</v>
+        <v>106.71</v>
       </c>
       <c r="J5" t="n">
-        <v>197.68</v>
+        <v>134.4</v>
       </c>
       <c r="K5" t="n">
-        <v>100.5</v>
+        <v>98.02</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>2.74</v>
+        <v>4.59</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="E6" t="n">
-        <v>25.05</v>
+        <v>6.29</v>
       </c>
       <c r="F6" t="n">
-        <v>2.07</v>
+        <v>4.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.21</v>
+        <v>4.34</v>
       </c>
       <c r="H6" t="n">
-        <v>2.43</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.02</v>
+        <v>4.84</v>
       </c>
       <c r="J6" t="n">
-        <v>4.18</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.11</v>
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
